--- a/decline_curve_history_matching.xlsx
+++ b/decline_curve_history_matching.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45B5A10B-3BAF-47FE-9B60-390E21199E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A439203-E217-44FA-A8C0-2DC383666532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="F3" s="5">
         <f>SUM(C8:C127)</f>
-        <v>21632.941447040244</v>
+        <v>20368.528344109895</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3201,12 +3201,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1">
-        <v>13</v>
+        <f>Data!A27</f>
+        <v>25</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
         <f t="shared" si="0"/>
-        <v>311.82491872728741</v>
+        <v>205.44915012185012</v>
       </c>
       <c r="D33" s="1"/>
     </row>
@@ -3356,12 +3357,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1">
-        <v>14</v>
+        <f>Data!A40</f>
+        <v>38</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
         <f t="shared" si="0"/>
-        <v>298.15397979650817</v>
+        <v>154.0845372875182</v>
       </c>
       <c r="D46" s="1"/>
     </row>
@@ -3511,12 +3513,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="1">
-        <v>15</v>
+        <f>Data!A53</f>
+        <v>51</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5">
         <f t="shared" si="0"/>
-        <v>285.7873043551416</v>
+        <v>125.0356163456765</v>
       </c>
       <c r="D59" s="1"/>
     </row>
@@ -3666,12 +3669,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="1">
-        <v>16</v>
+        <f>Data!A66</f>
+        <v>64</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5">
         <f t="shared" si="0"/>
-        <v>274.54008494624338</v>
+        <v>106.11053962569002</v>
       </c>
       <c r="D72" s="1"/>
     </row>
@@ -3821,12 +3825,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="1">
-        <v>17</v>
+        <f>Data!A79</f>
+        <v>77</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5">
         <f t="shared" si="2"/>
-        <v>264.26142311244587</v>
+        <v>92.693319052937525</v>
       </c>
       <c r="D85" s="1"/>
     </row>
@@ -3976,12 +3981,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="1">
-        <v>18</v>
+        <f>Data!A92</f>
+        <v>90</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5">
         <f t="shared" si="2"/>
-        <v>254.82682213770951</v>
+        <v>82.628564757755427</v>
       </c>
       <c r="D98" s="1"/>
     </row>
@@ -4131,12 +4137,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="1">
-        <v>19</v>
+        <f>Data!A105</f>
+        <v>103</v>
       </c>
       <c r="B111" s="5"/>
       <c r="C111" s="5">
         <f t="shared" si="2"/>
-        <v>246.13260122998909</v>
+        <v>74.767079718087601</v>
       </c>
       <c r="D111" s="1"/>
     </row>
@@ -4286,12 +4293,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="1">
-        <v>20</v>
+        <f>Data!A118</f>
+        <v>116</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5">
         <f t="shared" si="2"/>
-        <v>238.09167861298235</v>
+        <v>68.43690307844544</v>
       </c>
       <c r="D124" s="1"/>
     </row>
